--- a/out/Attention-S4_repeat_3_000007.xlsx
+++ b/out/Attention-S4_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.424137072939437</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.043559541701984</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.043559541701984</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.043559541701984</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.443559541701984</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.443559541701984</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.443559541701984</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002100831288443878</v>
+        <v>-6.038105188275221e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.421948127028575</v>
+        <v>0.6961042754547568</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.847640300331041</v>
+        <v>1.393284754049746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3631819254150858</v>
+        <v>0.1043839412694196</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.148805330513812</v>
+        <v>0.9050139873536248</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4540955785251447</v>
+        <v>0.1305139476654237</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.693872306174462</v>
+        <v>1.061674472939382</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6509440209870913</v>
+        <v>0.1870911250288232</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.541920922439834</v>
+        <v>1.305416430128927</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6963808155445422</v>
+        <v>0.2001504448110093</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.283787762410445</v>
+        <v>1.518640143900103</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7380240401696273</v>
+        <v>0.2121183915624241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.063507026267178</v>
+        <v>1.742743104207468</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3330565229857265</v>
+        <v>0.09572575083263495</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.99098273702379</v>
+        <v>1.721898468050247</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1608510777403759</v>
+        <v>0.04623051919669491</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.979367207694776</v>
+        <v>1.71855998084306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07664013680631405</v>
+        <v>0.02202746602705347</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.971669892232851</v>
+        <v>1.716347619634103</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02270830112826692</v>
+        <v>0.006523580880987169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.940363494360191</v>
+        <v>1.707346355452162</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01502026901061313</v>
+        <v>0.004313887701662389</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.947684299697426</v>
+        <v>1.709447096823808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00768460924275484</v>
+        <v>0.002204963193759101</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.948025297705177</v>
+        <v>1.709541551479308</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003929035633194641</v>
+        <v>0.001125481580367856</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.948193200862457</v>
+        <v>1.709586259537464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001473953128175555</v>
+        <v>0.0004203693234568383</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.947209091033932</v>
+        <v>1.70929965271882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008010308397816547</v>
+        <v>0.0002268266796096673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.947336375701847</v>
+        <v>1.709332699793215</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003828282158724643</v>
+        <v>0.000106262193078166</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.947301286837106</v>
+        <v>1.709319046125635</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002350850486541498</v>
+        <v>6.387685822045283e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.94738863681855</v>
+        <v>1.70934067507415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001205830372132251</v>
+        <v>3.10279205119908e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.947394623821581</v>
+        <v>1.709338859507548</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.594468097789584e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.947385821212778</v>
+        <v>1.709332746370905</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.465353771064406e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.947398157244825</v>
+        <v>1.709332779412467</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.947389612185392</v>
+        <v>1.70932675070418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.947382419672508</v>
+        <v>1.709321066170152</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.947378081135234</v>
+        <v>1.709316314894938</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.947372502840111</v>
+        <v>1.709311025747376</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.947367456219043</v>
+        <v>1.709311003013075</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.947367774499259</v>
+        <v>1.709311321293292</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.947368865745716</v>
+        <v>1.709312412539749</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.94736817613858</v>
+        <v>1.709311722932613</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.947368206450982</v>
+        <v>1.709311753245014</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.947368016998472</v>
+        <v>1.709311563792504</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.947368070045175</v>
+        <v>1.709311616839207</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.947368123091877</v>
+        <v>1.70931166988591</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.947368085201375</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.947367956373668</v>
+        <v>1.709311503167702</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.947367812389762</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.947367653249653</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.947367706296355</v>
+        <v>1.709311253090388</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.947367653249653</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.947367653249653</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.947367471375244</v>
+        <v>1.709311018169276</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.947367638093452</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.947367835124062</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.947367675983954</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.947367713874455</v>
+        <v>1.709311260668489</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.947367910905066</v>
+        <v>1.709311457699099</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.947367888170764</v>
+        <v>1.709311434964798</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.947367736608757</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.947367660827753</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.947367759343059</v>
+        <v>1.709311306137091</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.947367766921159</v>
+        <v>1.709311313715192</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.947368032154673</v>
+        <v>1.709311578948705</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.947367736608757</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.94736797910797</v>
+        <v>1.709311525902003</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.947368062467074</v>
+        <v>1.709311609261107</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.947367895748866</v>
+        <v>1.709311442542898</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.947368085201375</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.947367736608757</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.947367532000047</v>
+        <v>1.709311078794079</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.947367645671552</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.947367660827753</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.947367425906641</v>
+        <v>1.709310972700674</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.947367486531444</v>
+        <v>1.709311033325477</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.947367357703737</v>
+        <v>1.70931090449777</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.947367494109545</v>
+        <v>1.709311040903577</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.947367668405853</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.947367812389762</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.947367645671552</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.947367638093452</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.947367350125637</v>
+        <v>1.70931089691967</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.947367365281838</v>
+        <v>1.709310912075871</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.947367592624849</v>
+        <v>1.709311139418882</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.947367577468649</v>
+        <v>1.709311124262682</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.947367683562054</v>
+        <v>1.709311230356087</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.947367410750441</v>
+        <v>1.709310957544473</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.947367509265745</v>
+        <v>1.709311056059778</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.947367660827753</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.947367675983954</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.947367653249653</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.947367736608757</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.947367835124062</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.947367668405853</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.947367653249653</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.947367622937251</v>
+        <v>1.709311169731284</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.947367607781051</v>
+        <v>1.709311154575083</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.947367645671552</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.947367660827753</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.947367653249653</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000007.xlsx
+++ b/out/Attention-S4_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.443559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002100831288443878</v>
+        <v>-0.0001881226360371802</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.421948127028575</v>
+        <v>2.168776078530689</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.847640300331041</v>
+        <v>4.340904845037933</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3631819254150858</v>
+        <v>0.3252176473991269</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.148805330513812</v>
+        <v>2.81965315939957</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4540955785251447</v>
+        <v>0.4066279349686471</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.693872306174462</v>
+        <v>3.307742983394669</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6509440209870913</v>
+        <v>0.5828990537096419</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.541920922439834</v>
+        <v>4.067142959590771</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6963808155445422</v>
+        <v>0.6235868750099344</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.283787762410445</v>
+        <v>4.731460790481081</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7380240401696273</v>
+        <v>0.6608763977545571</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.063507026267178</v>
+        <v>5.429673897792648</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3330565229857265</v>
+        <v>0.2982412268154231</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.99098273702379</v>
+        <v>5.364730768008063</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1608510777403759</v>
+        <v>0.1440362378144105</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.979367207694776</v>
+        <v>5.35432944224792</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07664013680631405</v>
+        <v>0.0686295919823411</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.971669892232851</v>
+        <v>5.347436716309932</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02270830112826692</v>
+        <v>0.02033446938086828</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.940363494360191</v>
+        <v>5.319402959606993</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01502026901061313</v>
+        <v>0.01344958961944546</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.947684299697426</v>
+        <v>5.325957955596071</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00768460924275484</v>
+        <v>0.006880717911810413</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.948025297705177</v>
+        <v>5.32626278446775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003929035633194641</v>
+        <v>0.003517310818973401</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.948193200862457</v>
+        <v>5.326412614813957</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001473953128175555</v>
+        <v>0.001319548605070226</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.947209091033932</v>
+        <v>5.325530725254121</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008010308397816547</v>
+        <v>0.0007168802301012772</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.947336375701847</v>
+        <v>5.325644199240227</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003828282158724643</v>
+        <v>0.0003422969883939895</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.947301286837106</v>
+        <v>5.325612251740588</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002350850486541498</v>
+        <v>0.0002104861707182738</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.94738863681855</v>
+        <v>5.325689969592377</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001205830372132251</v>
+        <v>0.0001072012381659142</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.947394623821581</v>
+        <v>5.325694790694198</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.594468097789584e-05</v>
+        <v>4.995012219318478e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.947385821212778</v>
+        <v>5.325686389443345</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.465353771064406e-05</v>
+        <v>2.953695219959321e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.947398157244825</v>
+        <v>5.325696768957745</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>1.131855788691358e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.947389612185392</v>
+        <v>5.325688566329013</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>2.205584102398162e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.947382419672508</v>
+        <v>5.32568164788024</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.947378081135234</v>
+        <v>5.325677227336389</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.947372502840111</v>
+        <v>5.325671649041265</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.947367456219043</v>
+        <v>5.325666602420198</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.947367774499259</v>
+        <v>5.325666920700414</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.947368865745716</v>
+        <v>5.325668011946871</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.94736817613858</v>
+        <v>5.325667322339735</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.947368206450982</v>
+        <v>5.325667352652137</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.947368016998472</v>
+        <v>5.325667163199626</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.947368070045175</v>
+        <v>5.32566721624633</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.947368123091877</v>
+        <v>5.325667269293032</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.947368085201375</v>
+        <v>5.32566723140253</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.947367956373668</v>
+        <v>5.325667102574823</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.947367812389762</v>
+        <v>5.325666958590916</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.947367653249653</v>
+        <v>5.325666799450808</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.947367706296355</v>
+        <v>5.325666852497511</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.947367653249653</v>
+        <v>5.325666799450808</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.947367653249653</v>
+        <v>5.325666799450808</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.947367471375244</v>
+        <v>5.325666617576399</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.947367638093452</v>
+        <v>5.325666784294607</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.947367835124062</v>
+        <v>5.325666981325218</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.947367675983954</v>
+        <v>5.325666822185109</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.947367713874455</v>
+        <v>5.325666860075611</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.947367910905066</v>
+        <v>5.325667057106221</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.947367888170764</v>
+        <v>5.32566703437192</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.947367736608757</v>
+        <v>5.325666882809912</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.947367660827753</v>
+        <v>5.325666807028909</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.947367759343059</v>
+        <v>5.325666905544214</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.947367766921159</v>
+        <v>5.325666913122314</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.947368032154673</v>
+        <v>5.325667178355828</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.947367736608757</v>
+        <v>5.325666882809912</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.94736797910797</v>
+        <v>5.325667125309125</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.947368062467074</v>
+        <v>5.32566720866823</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.947367895748866</v>
+        <v>5.32566704195002</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.947368085201375</v>
+        <v>5.32566723140253</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.947367736608757</v>
+        <v>5.325666882809912</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.947367532000047</v>
+        <v>5.325666678201201</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.947367645671552</v>
+        <v>5.325666791872707</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.947367660827753</v>
+        <v>5.325666807028909</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.947367425906641</v>
+        <v>5.325666572107797</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.947367486531444</v>
+        <v>5.325666632732599</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.947367357703737</v>
+        <v>5.325666503904892</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.947367494109545</v>
+        <v>5.3256666403107</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242511</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.947367668405853</v>
+        <v>5.325666814607009</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.947367812389762</v>
+        <v>5.325666958590916</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.947367645671552</v>
+        <v>5.325666791872707</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.947367638093452</v>
+        <v>5.325666784294607</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.947367350125637</v>
+        <v>5.325666496326792</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.947367365281838</v>
+        <v>5.325666511482993</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.947367592624849</v>
+        <v>5.325666738826005</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.947367577468649</v>
+        <v>5.325666723669804</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.947367683562054</v>
+        <v>5.325666829763209</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.947367410750441</v>
+        <v>5.325666556951595</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.947367509265745</v>
+        <v>5.3256666554669</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.947367660827753</v>
+        <v>5.325666807028909</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.947367675983954</v>
+        <v>5.325666822185109</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.947367653249653</v>
+        <v>5.325666799450808</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.947367736608757</v>
+        <v>5.325666882809912</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.947367835124062</v>
+        <v>5.325666981325218</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.947367668405853</v>
+        <v>5.325666814607009</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.947367653249653</v>
+        <v>5.325666799450808</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.947367622937251</v>
+        <v>5.325666769138406</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.947367607781051</v>
+        <v>5.325666753982206</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.947367645671552</v>
+        <v>5.325666791872707</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.947367660827753</v>
+        <v>5.325666807028909</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.947367653249653</v>
+        <v>5.325666799450808</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000007.xlsx
+++ b/out/Attention-S4_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.005990665405988693</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005943045020103455</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.006085515022277832</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.003425441682338715</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.005643460899591446</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.004266683012247086</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004658307880163193</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.004049059003591537</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002852886915206909</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003009442239999771</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.002842031419277191</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001988299190998077</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0007993727922439575</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001196384429931641</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0005370564758777618</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0001448243856430054</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0008353441953659058</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001074448227882385</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001585375517606735</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002486120909452438</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003447495400905609</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.004904180765151978</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00363435223698616</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.00310487300157547</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002693016082048416</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.355583685738504</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002401750534772873</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002205684781074524</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002418175339698792</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0018770731985569</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001873437315225601</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001405175775289536</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0009871162474155426</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001226451247930527</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0007131472229957581</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.155583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001887407153844833</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.155583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01115786656737328</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.155583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003527499735355377</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.155583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002178583294153214</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.155583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001881226360371802</v>
+        <v>-0.0001335535717869643</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.168776078530689</v>
+        <v>1.539675436723744</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.00101446732878685</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.340904845037933</v>
+        <v>3.081730933809367</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3252176473991269</v>
+        <v>0.2308811771930159</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0002745054662227631</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.81965315939957</v>
+        <v>2.001751440677884</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4066279349686471</v>
+        <v>0.2886765953680197</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.002032585442066193</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.307742983394669</v>
+        <v>2.348260187964887</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5828990537096419</v>
+        <v>0.4138166931146126</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.004287503659725189</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.067142959590771</v>
+        <v>2.887379778388652</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6235868750099344</v>
+        <v>0.4427015448511257</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.009919282048940659</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.155583685738504</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.731460790481081</v>
+        <v>3.358997725057585</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6608763977545571</v>
+        <v>0.4691744069131162</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01806629821658134</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.429673897792648</v>
+        <v>3.854679273798357</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2982412268154231</v>
+        <v>0.2117296837708128</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01818610727787018</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.364730768008063</v>
+        <v>3.808574208374842</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1440362378144105</v>
+        <v>0.1022564029922444</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.003954727202653885</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.35432944224792</v>
+        <v>3.801189972815334</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0686295919823411</v>
+        <v>0.04872151876334413</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.007615473121404648</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.347436716309932</v>
+        <v>3.79629662831082</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02033446938086828</v>
+        <v>0.01443562508945342</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004022493958473206</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7001101738204644</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.319402959606993</v>
+        <v>3.77639381926476</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01344958961944546</v>
+        <v>0.009546922343961529</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.00116928294301033</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.325957955596071</v>
+        <v>3.781046008672738</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006880717911810413</v>
+        <v>0.00488328902341728</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.005718868225812912</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.32626278446775</v>
+        <v>3.781260968087588</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003517310818973401</v>
+        <v>0.002495548749451251</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001417160034179688</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.326412614813957</v>
+        <v>3.78136589139576</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001319548605070226</v>
+        <v>0.000935051067141269</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003884721547365189</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.325530725254121</v>
+        <v>3.780738300270838</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007168802301012772</v>
+        <v>0.0005073287118775922</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.006136506795883179</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.325644199240227</v>
+        <v>3.780817451154166</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003422969883939895</v>
+        <v>0.0002421610146236401</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.006164424121379852</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.325612251740588</v>
+        <v>3.780793294986589</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002104861707182738</v>
+        <v>0.0001475130432024312</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002075508236885071</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.325689969592377</v>
+        <v>3.780847029037397</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001072012381659142</v>
+        <v>7.529079428386522e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.007606327533721924</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.325694790694198</v>
+        <v>3.780849024444655</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.995012219318478e-05</v>
+        <v>3.396463210062193e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01864241063594818</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.325686389443345</v>
+        <v>3.780841612648595</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.953695219959321e-05</v>
+        <v>1.930378117749152e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.006321821361780167</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.325696768957745</v>
+        <v>3.780847518348274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.131855788691358e-05</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.005780801177024841</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.044636661902425</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.325688566329013</v>
+        <v>3.780840230756323</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.006908006966114044</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.32568164788024</v>
+        <v>3.78083386043577</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003417655825614929</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.325677227336389</v>
+        <v>3.780829274526238</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003381494432687759</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.325671649041265</v>
+        <v>3.780823841394769</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001615807414054871</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.325666602420198</v>
+        <v>3.780818794773702</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0171985812485218</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.325666920700414</v>
+        <v>3.780819113053918</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.03862321004271507</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.355583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.325668011946871</v>
+        <v>3.780820204300375</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0120021291077137</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.325667322339735</v>
+        <v>3.780819514693239</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.000605899840593338</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.044636661902425</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.325667352652137</v>
+        <v>3.780819545005641</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002276849001646042</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.044636661902425</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.325667163199626</v>
+        <v>3.780819355553131</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.0008382759988307953</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.32566721624633</v>
+        <v>3.780819408599834</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005159217864274979</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.325667269293032</v>
+        <v>3.780819461646536</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01105305179953575</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.32566723140253</v>
+        <v>3.780819423756034</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.007592126727104187</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.325667102574823</v>
+        <v>3.780819294928327</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00813906267285347</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.325666958590916</v>
+        <v>3.78081915094442</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.009674113243818283</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.325666799450808</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.005404911935329437</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.325666852497511</v>
+        <v>3.780819044851015</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004976768046617508</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.325666799450808</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.00495930016040802</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.325666799450808</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.005412936210632324</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.325666617576399</v>
+        <v>3.780818809929903</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003760620951652527</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.325666784294607</v>
+        <v>3.780818976648111</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.007038440555334091</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.325666981325218</v>
+        <v>3.780819173678721</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.009930800646543503</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.325666822185109</v>
+        <v>3.780819014538613</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001590825617313385</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.325666860075611</v>
+        <v>3.780819052429115</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0009888261556625366</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.325667057106221</v>
+        <v>3.780819249459725</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005536634474992752</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.32566703437192</v>
+        <v>3.780819226725424</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003606211394071579</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.325666882809912</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.001081831753253937</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.325666807028909</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0003837384283542633</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.04463666190242505</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.325666905544214</v>
+        <v>3.780819097897718</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0011618472635746</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.325666913122314</v>
+        <v>3.780819105475818</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.001707594841718674</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.325667178355828</v>
+        <v>3.780819370709332</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.002219513058662415</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.325666882809912</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.005215596407651901</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.325667125309125</v>
+        <v>3.780819317662628</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.002158354967832565</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.32566720866823</v>
+        <v>3.780819401021733</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01546376571059227</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.32566704195002</v>
+        <v>3.780819234303525</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.006304625421762466</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.32566723140253</v>
+        <v>3.780819423756034</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0006410926580429077</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.325666882809912</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004464965313673019</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.325666678201201</v>
+        <v>3.780818870554705</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0005352459847927094</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.325666791872707</v>
+        <v>3.780818984226211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.001214932650327682</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.325666807028909</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.004054319113492966</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.325666572107797</v>
+        <v>3.7808187644613</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.004571270197629929</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.325666632732599</v>
+        <v>3.780818825086103</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002860881388187408</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.325666503904892</v>
+        <v>3.780818696258396</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.004206478595733643</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.3256666403107</v>
+        <v>3.780818832664204</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.00390901044011116</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.04463666190242511</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.325666814607009</v>
+        <v>3.780819006960512</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.001077644526958466</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.325666958590916</v>
+        <v>3.78081915094442</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0004944950342178345</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.325666791872707</v>
+        <v>3.780818984226211</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002131130546331406</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.325666784294607</v>
+        <v>3.780818976648111</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002834424376487732</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.325666496326792</v>
+        <v>3.780818688680296</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002315875142812729</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.325666511482993</v>
+        <v>3.780818703836497</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004842605441808701</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.325666738826005</v>
+        <v>3.780818931179509</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002497058361768723</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.325666723669804</v>
+        <v>3.780818916023307</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003539718687534332</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.325666829763209</v>
+        <v>3.780819022116713</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.00300867110490799</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.325666556951595</v>
+        <v>3.780818749305099</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.001172717660665512</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.16</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.3256666554669</v>
+        <v>3.780818847820404</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.002897296100854874</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.325666807028909</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.003211863338947296</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.325666822185109</v>
+        <v>3.780819014538613</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.001989308744668961</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.325666799450808</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0007938183844089508</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.325666882809912</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.001425277441740036</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.044636661902425</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.325666981325218</v>
+        <v>3.780819173678721</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.000994514673948288</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.325666814607009</v>
+        <v>3.780819006960512</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.001865383237600327</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.325666799450808</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.001545466482639313</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.325666769138406</v>
+        <v>3.78081896149191</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001118123531341553</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.325666753982206</v>
+        <v>3.78081894633571</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001513633877038956</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.325666791872707</v>
+        <v>3.780818984226211</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0003929398953914642</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.325666807028909</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002829529345035553</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.325666799450808</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000007.xlsx
+++ b/out/Attention-S4_repeat_3_000007.xlsx
@@ -65339,7 +65339,7 @@
         <v>-0.007038440555334091</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>3.780819173678721</v>
@@ -66134,7 +66134,7 @@
         <v>-0.009930800646543503</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>3.780819014538613</v>
@@ -66929,7 +66929,7 @@
         <v>-0.001590825617313385</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>3.780819052429115</v>
@@ -67724,7 +67724,7 @@
         <v>-0.0009888261556625366</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>3.780819249459725</v>
@@ -68519,7 +68519,7 @@
         <v>-0.005536634474992752</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>3.780819226725424</v>
@@ -69314,7 +69314,7 @@
         <v>-0.003606211394071579</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
         <v>3.780819075163416</v>
@@ -70109,7 +70109,7 @@
         <v>-0.001081831753253937</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
         <v>3.780818999382412</v>
@@ -70904,7 +70904,7 @@
         <v>0.0003837384283542633</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>3.780819097897718</v>
@@ -71699,7 +71699,7 @@
         <v>-0.0011618472635746</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>3.780819105475818</v>
